--- a/output/pdf_financials_xlsx/NILI.xlsx
+++ b/output/pdf_financials_xlsx/NILI.xlsx
@@ -4184,13 +4184,13 @@
         <v>4.008666</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>13.209853</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>17.667849</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>21.275914</v>
       </c>
     </row>
     <row r="93">
@@ -7003,7 +7003,11 @@
           <t>Reserve 8</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -7561,7 +7565,11 @@
           <t>Reserve 7</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NILI.xlsx
+++ b/output/pdf_financials_xlsx/NILI.xlsx
@@ -852,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-2.5e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-4.3e-05</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -873,13 +873,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.170106</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.059597</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.004553</v>
       </c>
     </row>
     <row r="13">
@@ -1496,10 +1496,10 @@
         <v>-0.449769</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.459756</v>
+        <v>-0.459731</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.459756</v>
+        <v>-0.459713</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.308641</v>
@@ -1517,13 +1517,13 @@
         <v>-2.972814</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-8.929486000000001</v>
+        <v>-9.099591999999999</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-9.846355000000001</v>
+        <v>-9.905951999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.655717</v>
+        <v>-6.66027</v>
       </c>
     </row>
     <row r="28">
@@ -1576,10 +1576,10 @@
         <v>-0.449769</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.459756</v>
+        <v>-0.459731</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.459756</v>
+        <v>-0.459713</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.308641</v>
@@ -1597,13 +1597,13 @@
         <v>-2.972814</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-8.929486000000001</v>
+        <v>-9.099591999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-9.846355000000001</v>
+        <v>-9.905951999999999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.655717</v>
+        <v>-6.66027</v>
       </c>
     </row>
     <row r="30">
@@ -1799,22 +1799,22 @@
         <v>0.282236</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.104489</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.969954</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.020621</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.328479</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.914069</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.693871</v>
       </c>
     </row>
     <row r="35">
@@ -1879,22 +1879,22 @@
         <v>0.282236</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.104489</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>3.969954</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.020621</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>3.038614</v>
+        <v>6.367093</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.003707</v>
+        <v>1.917776</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>3</v>
+        <v>5.693871</v>
       </c>
     </row>
     <row r="37">
@@ -2359,22 +2359,22 @@
         <v>0.010376</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.233362</v>
+        <v>0.128873</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.301657</v>
+        <v>0.331703</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.106974</v>
+        <v>0.086353</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.761818</v>
+        <v>0.433339</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.114189</v>
+        <v>0.20012</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.808876</v>
+        <v>0.115005</v>
       </c>
     </row>
     <row r="49">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -25780,7 +25780,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -31467,7 +31467,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">

--- a/output/pdf_financials_xlsx/NILI.xlsx
+++ b/output/pdf_financials_xlsx/NILI.xlsx
@@ -655,19 +655,19 @@
         <v>0.335205</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.284876</v>
+        <v>0.324563</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.118616</v>
+        <v>0.122273</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.135447</v>
+        <v>0.146419</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.077282</v>
+        <v>0.09574100000000001</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.086629</v>
+        <v>0.13866</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.647884</v>
@@ -775,19 +775,19 @@
         <v>0.349761</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.317632</v>
+        <v>0.357319</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.22749</v>
+        <v>0.231147</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.5432630000000001</v>
+        <v>0.554235</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.378612</v>
+        <v>0.397071</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.087808</v>
+        <v>0.139839</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.683547</v>
@@ -3135,13 +3135,13 @@
         <v>0.228644</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.053598</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.058056</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0.02</v>
@@ -3175,13 +3175,13 @@
         <v>0.457288</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.425748</v>
+        <v>0.479346</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.115154</v>
+        <v>0.150154</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.187374</v>
+        <v>0.24543</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.070271</v>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.798088</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -17039,7 +17039,11 @@
           <t>Proceeds from sale of marketable securities 8</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -17183,7 +17187,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -26770,7 +26778,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -28138,7 +28150,11 @@
           <t>Office expenses 9</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -29568,7 +29584,11 @@
           <t>Office expenses 11</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
